--- a/data/trans_dic/ProbViv_estruc-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,19; 41,58</t>
+          <t>12,51; 40,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,46; 35,51</t>
+          <t>16,05; 36,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,3; 33,55</t>
+          <t>17,25; 33,32</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 11,67</t>
+          <t>6,39; 11,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 11,68</t>
+          <t>7,08; 11,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 10,78</t>
+          <t>7,4; 10,88</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 12,35</t>
+          <t>5,08; 12,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,72</t>
+          <t>3,0; 9,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,62</t>
+          <t>4,83; 9,62</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,42</t>
+          <t>7,79; 12,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,81</t>
+          <t>7,82; 11,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 11,23</t>
+          <t>8,32; 11,37</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>12650</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15575</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28226</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6841; 22071</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9950; 22323</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20129; 38874</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>40181</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47336</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>87517</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>29409; 52264</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36569; 60417</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>72263; 106264</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11975</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10418</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22392</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7540; 19108</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5477; 17618</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15987; 31849</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>64805</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>73329</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>138135</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>51732; 82928</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>59503; 88982</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>118573; 161934</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/ProbViv_estruc-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,51; 40,37</t>
+          <t>12,87; 41,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,05; 36,0</t>
+          <t>15,93; 35,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,25; 33,32</t>
+          <t>16,84; 33,19</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 11,35</t>
+          <t>6,49; 11,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 11,69</t>
+          <t>7,22; 11,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,88</t>
+          <t>7,3; 10,64</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 12,86</t>
+          <t>4,72; 12,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,66</t>
+          <t>3,22; 9,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 9,62</t>
+          <t>4,56; 9,52</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,49</t>
+          <t>7,75; 12,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 11,69</t>
+          <t>7,63; 11,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 11,37</t>
+          <t>8,26; 11,38</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6841; 22071</t>
+          <t>7039; 22923</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9950; 22323</t>
+          <t>9875; 21963</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20129; 38874</t>
+          <t>19649; 38723</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29409; 52264</t>
+          <t>29902; 52708</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36569; 60417</t>
+          <t>37308; 61086</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72263; 106264</t>
+          <t>71292; 104013</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7540; 19108</t>
+          <t>7012; 18082</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5477; 17618</t>
+          <t>5877; 17641</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15987; 31849</t>
+          <t>15107; 31501</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51732; 82928</t>
+          <t>51471; 83043</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59503; 88982</t>
+          <t>58030; 90503</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118573; 161934</t>
+          <t>117698; 162192</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_estruc-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,87; 41,92</t>
+          <t>15,84; 35,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,93; 35,42</t>
+          <t>13,22; 36,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,84; 33,19</t>
+          <t>17,36; 32,04</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,45</t>
+          <t>7,16; 12,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 11,82</t>
+          <t>7,04; 11,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,64</t>
+          <t>7,58; 10,8</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 12,17</t>
+          <t>3,15; 9,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,67</t>
+          <t>4,93; 12,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 9,52</t>
+          <t>4,8; 9,83</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 12,51</t>
+          <t>7,84; 11,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 11,89</t>
+          <t>7,9; 12,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,26; 11,38</t>
+          <t>8,54; 11,19</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28226</t>
+          <t>24860</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7039; 22923</t>
+          <t>8989; 19949</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9875; 21963</t>
+          <t>6183; 17280</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19649; 38723</t>
+          <t>17963; 33161</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>40181</t>
+          <t>44380</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>38574</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87517</t>
+          <t>82953</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29902; 52708</t>
+          <t>34081; 57085</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37308; 61086</t>
+          <t>30459; 48790</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71292; 104013</t>
+          <t>68806; 98082</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>21726</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7012; 18082</t>
+          <t>5282; 16583</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5877; 17641</t>
+          <t>7342; 18394</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15107; 31501</t>
+          <t>15201; 31089</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>64805</t>
+          <t>68184</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>73329</t>
+          <t>61356</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>138135</t>
+          <t>129539</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51471; 83043</t>
+          <t>54905; 83074</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58030; 90503</t>
+          <t>49590; 75846</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>117698; 162192</t>
+          <t>113405; 148609</t>
         </is>
       </c>
     </row>
